--- a/artfynd/A 13645-2025 artfynd.xlsx
+++ b/artfynd/A 13645-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303497</v>
+        <v>123303593</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636520</v>
+        <v>636637</v>
       </c>
       <c r="R3" t="n">
-        <v>7188000</v>
+        <v>7187668</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123303593</v>
+        <v>123303497</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636637</v>
+        <v>636520</v>
       </c>
       <c r="R4" t="n">
-        <v>7187668</v>
+        <v>7188000</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 13645-2025 artfynd.xlsx
+++ b/artfynd/A 13645-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123303593</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>123303497</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13645-2025 artfynd.xlsx
+++ b/artfynd/A 13645-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303593</v>
+        <v>123303497</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636637</v>
+        <v>636520</v>
       </c>
       <c r="R3" t="n">
-        <v>7187668</v>
+        <v>7188000</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123303497</v>
+        <v>123303593</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636520</v>
+        <v>636637</v>
       </c>
       <c r="R4" t="n">
-        <v>7188000</v>
+        <v>7187668</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 13645-2025 artfynd.xlsx
+++ b/artfynd/A 13645-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123303497</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>123303593</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13645-2025 artfynd.xlsx
+++ b/artfynd/A 13645-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>103223895</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636410.8959345681</v>
+        <v>636411</v>
       </c>
       <c r="R2" t="n">
-        <v>7188000.055747504</v>
+        <v>7188000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +787,7 @@
         <v>123303497</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,12 +896,7 @@
         <v>123303593</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
